--- a/artfynd/A 25699-2022 artfynd.xlsx
+++ b/artfynd/A 25699-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86864846</v>
+        <v>137457201</v>
       </c>
       <c r="B2" t="n">
-        <v>99142</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grönåsen vägen, Dlr</t>
+          <t>Grönåsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541331</v>
+        <v>541141</v>
       </c>
       <c r="R2" t="n">
-        <v>6680749</v>
+        <v>6681250</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,61 +759,60 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>öppen våtmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Jansson, Lena Stigsdotter</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86864846</t>
+          <t>https://artportalen.se/Sighting/137457201</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86865210</v>
+        <v>86864846</v>
       </c>
       <c r="B3" t="n">
-        <v>109815</v>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -898,16 +893,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86865210</t>
+          <t>https://artportalen.se/Sighting/86864846</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88170162</v>
+        <v>86865210</v>
       </c>
       <c r="B4" t="n">
-        <v>102560</v>
+        <v>109815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222133</v>
+        <v>220204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -933,19 +928,23 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grönåsen, Dlr</t>
+          <t>Grönåsen vägen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541285</v>
+        <v>541331</v>
       </c>
       <c r="R4" t="n">
-        <v>6680837</v>
+        <v>6680749</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,60 +982,61 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Traktorväg-granskog</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bonnie Nilzon</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bonnie Nilzon, Karin Nilzon, Birgitta Pettersson Frank</t>
+          <t>Staffan Jansson, Lena Stigsdotter</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88170162</t>
+          <t>https://artportalen.se/Sighting/86865210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88170159</v>
+        <v>88170162</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>102560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541158</v>
+        <v>541285</v>
       </c>
       <c r="R5" t="n">
-        <v>6681004</v>
+        <v>6680837</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Torpruin</t>
+          <t>Traktorväg-granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1112,16 +1112,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88170159</t>
+          <t>https://artportalen.se/Sighting/88170162</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86864878</v>
+        <v>88170159</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,37 +1129,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grönåsen vägen, Dlr</t>
+          <t>Grönåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541331</v>
+        <v>541158</v>
       </c>
       <c r="R6" t="n">
-        <v>6680749</v>
+        <v>6681004</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,28 +1197,135 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Torpruin</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Bonnie Nilzon</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Staffan Jansson, Lena Stigsdotter</t>
+          <t>Bonnie Nilzon, Karin Nilzon, Birgitta Pettersson Frank</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88170159</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86864878</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grönåsen vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>541331</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6680749</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Jansson, Lena Stigsdotter</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86864878</t>
         </is>
@@ -1231,6 +1338,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25699-2022 artfynd.xlsx
+++ b/artfynd/A 25699-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137457201</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
